--- a/reports/AI_Strategy_Report.xlsx
+++ b/reports/AI_Strategy_Report.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t xml:space="preserve">ABC </t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Customer Support</t>
+          <t>Inventory Management</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>salary</t>
+          <t xml:space="preserve">salary
+</t>
         </is>
       </c>
     </row>
@@ -576,7 +577,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Increase Revenue</t>
+          <t>Reduce Costs</t>
         </is>
       </c>
     </row>
@@ -591,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,17 +750,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Customer Support AI</t>
+          <t>Customer Churn Prediction</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LLM + RAG</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Support Tickets;Customer Data</t>
+          <t>Customer Data;Sales Data</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -779,7 +780,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Automate customer questions and support responses</t>
+          <t>Identify customers likely to stop purchasing</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -799,17 +800,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Customer Churn Prediction</t>
+          <t>Customer Support AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>LLM + RAG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Customer Data;Sales Data</t>
+          <t>Support Tickets;Customer Data</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -829,7 +830,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Identify customers likely to stop purchasing</t>
+          <t>Automate customer questions and support responses</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -849,17 +850,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Demand Forecasting</t>
+          <t>AI Customer Service Agent</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>AI Agents</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sales Data;Product Data</t>
+          <t>Customer Data;Support Data</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -879,53 +880,57 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Predict future product demand</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Autonomous AI agent that handles customer queries and support workflows</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Customer Data</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Recommendation System</t>
+          <t>AI Marketing Agent</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>AI Agents</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Customer Data;Product Data;Sales Data</t>
+          <t>Customer Data;Marketing Data</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Recommend relevant products to customers</t>
+          <t>AI agent that creates campaigns and automates marketing workflows</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -934,7 +939,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -945,50 +950,288 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Inventory Optimization</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Inventory Data;Sales Data;Product Data</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Optimize inventory levels and reduce stockouts</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sales Data;Product Data</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Predict future product demand</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Recommendation System</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Customer Data;Product Data;Sales Data</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Recommend relevant products to customers</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Customer Data</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Fraud Detection</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Transaction Data;Customer Data</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Detect potentially fraudulent transactions</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Customer Data</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I11" t="n">
         <v>3.2</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Sales Agent</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AI Agents</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Customer Data;Sales Data</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AI agent that assists customers and automates sales activities</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Customer Data</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Inventory Agent</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AI Agents</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Inventory Data;Sales Data</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AI agent that monitors inventory and coordinates replenishment workflows</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1074,7 +1317,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Demand Forecasting — Machine Learning</t>
+          <t>Inventory Optimization — Machine Learning</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1329,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recommendation System — Machine Learning</t>
+          <t>Demand Forecasting — Machine Learning</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1341,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Recommendation System — Machine Learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Phase 3 - Advanced ML</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Fraud Detection — Machine Learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Phase 4 - AI Agents</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AI Customer Service Agent — AI Agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Phase 4 - AI Agents</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AI Marketing Agent — AI Agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Phase 4 - AI Agents</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AI Sales Agent — AI Agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Phase 4 - AI Agents</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AI Inventory Agent — AI Agents</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,12 +1559,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Customer Support AI</t>
+          <t>Customer Churn Prediction</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LLM + RAG</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1274,7 +1577,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4–8 weeks</t>
+          <t>6–10 weeks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1284,29 +1587,29 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AI Developer + Backend Developer + Support Team</t>
+          <t>Data Scientist + Data Engineer + Marketing Team</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>['Collect support documents and FAQs', 'Clean and organize knowledge sources', 'Create document embeddings', 'Build RAG knowledge base', 'Connect an LLM', 'Develop customer support interface', 'Test responses', 'Deploy and monitor the system']</t>
+          <t>['Collect historical customer data', 'Identify customers who previously churned', 'Create customer behavior features', 'Train classification model', 'Evaluate model performance', 'Generate customer churn scores', 'Create retention workflows', 'Monitor model performance']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Faster customer responses and reduced support workload</t>
+          <t>Earlier identification of customers at risk of leaving</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Customer Churn Prediction</t>
+          <t>Customer Support AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>LLM + RAG</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1319,7 +1622,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6–10 weeks</t>
+          <t>4–8 weeks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1329,42 +1632,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Data Scientist + Data Engineer + Marketing Team</t>
+          <t>AI Developer + Backend Developer + Support Team</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>['Collect historical customer data', 'Identify customers who previously churned', 'Create customer behavior features', 'Train classification model', 'Evaluate model performance', 'Generate customer churn scores', 'Create retention workflows', 'Monitor model performance']</t>
+          <t>['Collect support documents and FAQs', 'Clean and organize knowledge sources', 'Create document embeddings', 'Build RAG knowledge base', 'Connect an LLM', 'Develop customer support interface', 'Test responses', 'Deploy and monitor the system']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Earlier identification of customers at risk of leaving</t>
+          <t>Faster customer responses and reduced support workload</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Demand Forecasting</t>
+          <t>AI Customer Service Agent</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>AI Agents</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6–10 weeks</t>
+          <t>8–12+ weeks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1374,33 +1677,33 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Data Scientist + Data Engineer + Business Analyst</t>
+          <t>AI Engineer + Backend Developer + Support Team</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>['Collect historical demand data', 'Clean and preprocess the data', 'Perform exploratory data analysis', 'Create forecasting features', 'Train forecasting models', 'Evaluate model performance', 'Deploy forecasting pipeline', 'Monitor prediction accuracy']</t>
+          <t>['Collect customer support data and FAQs', 'Organize customer and support knowledge sources', 'Build the agent knowledge base', 'Connect the LLM to the agent', 'Define customer service workflows', 'Connect order and customer information systems', 'Implement escalation to human support', 'Test agent responses and workflows', 'Deploy the customer service agent', 'Monitor conversations and agent performance']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Better demand planning and reduced stock-related problems</t>
+          <t>Automated customer assistance and reduced support workload</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Recommendation System</t>
+          <t>AI Marketing Agent</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>AI Agents</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,72 +1712,297 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8–12 weeks</t>
+          <t>8–12+ weeks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ML Engineer + Data Scientist + Backend Developer</t>
+          <t>AI Engineer + Marketing Specialist + Backend Developer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>['Collect customer interaction data', 'Prepare product and customer datasets', 'Analyze user behavior', 'Develop recommendation algorithm', 'Train and evaluate recommendation model', 'Integrate recommendations into the application', 'Run A/B testing', 'Monitor recommendation quality']</t>
+          <t>['Collect customer and marketing data', 'Organize marketing knowledge and brand guidelines', 'Connect the LLM to the marketing agent', 'Define campaign planning workflows', 'Build content generation capabilities', 'Connect marketing platforms', 'Implement campaign monitoring workflows', 'Add human approval before publishing', 'Test generated campaigns and content', 'Deploy and monitor the marketing agent']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>More personalized customer experiences and potential revenue growth</t>
+          <t>Faster campaign creation and reduced marketing workload</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Inventory Optimization</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>6–10 weeks</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Data Scientist + Data Engineer + Operations Team</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>['Collect inventory and transaction data', 'Analyze inventory patterns', 'Identify stock-out and overstock situations', 'Develop optimization model', 'Test recommendations', 'Integrate with inventory system', 'Monitor inventory performance']</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Reduced inventory costs and improved stock availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>6–10 weeks</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Data Scientist + Data Engineer + Business Analyst</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>['Collect historical demand data', 'Clean and preprocess the data', 'Perform exploratory data analysis', 'Create forecasting features', 'Train forecasting models', 'Evaluate model performance', 'Deploy forecasting pipeline', 'Monitor prediction accuracy']</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Better demand planning and reduced stock-related problems</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Recommendation System</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8–12 weeks</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ML Engineer + Data Scientist + Backend Developer</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>['Collect customer interaction data', 'Prepare product and customer datasets', 'Analyze user behavior', 'Develop recommendation algorithm', 'Train and evaluate recommendation model', 'Integrate recommendations into the application', 'Run A/B testing', 'Monitor recommendation quality']</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>More personalized customer experiences and potential revenue growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Fraud Detection</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C11" t="n">
         <v>3.2</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>8–12 weeks</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Data Scientist + ML Engineer + Security Team</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>['Collect historical transaction data', 'Identify fraudulent transactions', 'Engineer fraud detection features', 'Train machine learning models', 'Evaluate false positives and false negatives', 'Integrate real-time detection', 'Create fraud monitoring dashboard', 'Continuously retrain the model']</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Earlier detection of potentially fraudulent transactions</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Sales Agent</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AI Agents</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8–12+ weeks</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AI Engineer + Backend Developer + Sales Team</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>['Collect customer, product and sales data', 'Build product and customer knowledge base', 'Connect the LLM to the sales agent', 'Define lead qualification workflows', 'Implement product recommendation capabilities', 'Connect CRM and sales systems', 'Enable customer interaction workflows', 'Add human approval for important sales actions', 'Test sales conversations', 'Deploy and monitor the sales agent']</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Automated sales assistance and improved customer engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Inventory Agent</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AI Agents</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8–12+ weeks</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AI Engineer + Data Engineer + Operations Team</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>['Collect inventory, product and sales data', 'Build inventory knowledge base', 'Connect the LLM to the inventory agent', 'Define stock monitoring workflows', 'Detect low-stock and overstock situations', 'Connect inventory and procurement systems', 'Generate replenishment recommendations', 'Add human approval for inventory actions', 'Test inventory workflows', 'Deploy and monitor the inventory agent']</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Automated inventory monitoring and improved stock management</t>
         </is>
       </c>
     </row>
@@ -1489,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1538,6 +2066,11 @@
           <t>budget_status</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>budget_gap</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1575,6 +2108,9 @@
           <t>Above Budget</t>
         </is>
       </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1612,16 +2148,19 @@
           <t>Above Budget</t>
         </is>
       </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Customer Support AI</t>
+          <t>Customer Churn Prediction</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LLM + RAG</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1636,29 +2175,32 @@
         <v>250000</v>
       </c>
       <c r="F4" t="n">
-        <v>120000</v>
+        <v>144000</v>
       </c>
       <c r="G4" t="n">
-        <v>-52</v>
+        <v>-42.4</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>20.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>Above Budget</t>
         </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Customer Churn Prediction</t>
+          <t>Customer Support AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>LLM + RAG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1673,66 +2215,72 @@
         <v>250000</v>
       </c>
       <c r="F5" t="n">
-        <v>144000</v>
+        <v>120000</v>
       </c>
       <c r="G5" t="n">
-        <v>-42.4</v>
+        <v>-52</v>
       </c>
       <c r="H5" t="n">
-        <v>20.8</v>
+        <v>25</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Above Budget</t>
         </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Demand Forecasting</t>
+          <t>AI Customer Service Agent</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>AI Agents</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="E6" t="n">
         <v>300000</v>
       </c>
       <c r="F6" t="n">
-        <v>120000</v>
+        <v>144000</v>
       </c>
       <c r="G6" t="n">
-        <v>-60</v>
+        <v>-52</v>
       </c>
       <c r="H6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Above Budget</t>
         </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Recommendation System</t>
+          <t>AI Marketing Agent</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>AI Agents</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1741,61 +2289,267 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E7" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="F7" t="n">
-        <v>180000</v>
+        <v>120000</v>
       </c>
       <c r="G7" t="n">
-        <v>-64</v>
+        <v>-60</v>
       </c>
       <c r="H7" t="n">
-        <v>33.3</v>
+        <v>30</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>Above Budget</t>
         </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Inventory Optimization</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-60</v>
+      </c>
+      <c r="H8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Above Budget</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-60</v>
+      </c>
+      <c r="H9" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Above Budget</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Recommendation System</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-64</v>
+      </c>
+      <c r="H10" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Above Budget</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Fraud Detection</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>3.2</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E11" t="n">
         <v>500000</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F11" t="n">
         <v>144000</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G11" t="n">
         <v>-71.2</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H11" t="n">
         <v>41.7</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Above Budget</t>
         </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Sales Agent</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AI Agents</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-64</v>
+      </c>
+      <c r="H12" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Above Budget</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Inventory Agent</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AI Agents</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>144000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-64</v>
+      </c>
+      <c r="H13" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Above Budget</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
